--- a/healthcare_forms/041_summer_camp_health_questionnaire--healthcare_forms.xlsx
+++ b/healthcare_forms/041_summer_camp_health_questionnaire--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'peanut'}</t>
+          <t>peanut</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Peanut'}</t>
+          <t>Peanut</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'tree'}</t>
+          <t>tree</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Tree'}</t>
+          <t>Tree</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'shellfish'}</t>
+          <t>shellfish</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Shellfish'}</t>
+          <t>Shellfish</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'milk'}</t>
+          <t>milk</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Milk'}</t>
+          <t>Milk</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'eggs'}</t>
+          <t>eggs</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Eggs'}</t>
+          <t>Eggs</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'wheat'}</t>
+          <t>wheat</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'Wheat'}</t>
+          <t>Wheat</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'soy'}</t>
+          <t>soy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'Soy'}</t>
+          <t>Soy</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'fish'}</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'Fish'}</t>
+          <t>Fish</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'crustacean'}</t>
+          <t>crustacean</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'Crustacean'}</t>
+          <t>Crustacean</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'sulfites'}</t>
+          <t>sulfites</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'Sulfites'}</t>
+          <t>Sulfites</t>
         </is>
       </c>
     </row>
